--- a/forms/trg/Formulir_TRG_tfed.xlsx
+++ b/forms/trg/Formulir_TRG_tfed.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Rachmat Hidayat</t>
+          <t>Prof. Mukti Zainuddin</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Fisheries Remote Sensing</t>
+          <t>Satellite oceanography and marine fisheries …</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -938,12 +934,12 @@
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6790267</t>
+          <t>5975402</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57200559829</t>
+          <t>6506490325</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Musbir</t>
+          <t>Dr. Rachmat Hidayat</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +969,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Fisheries Oceanography</t>
+          <t>Fisheries Remote Sensing</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -983,12 +979,12 @@
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6078490</t>
+          <t>6790267</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57201492379</t>
+          <t>57200559829</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Aisjah Farhum</t>
+          <t>Prof. Musbir</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1018,7 +1014,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Fishing vessel engineering</t>
+          <t>Fisheries Oceanography</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1028,12 +1024,12 @@
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6005387</t>
+          <t>6078490</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57195941968</t>
+          <t>57201492379</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Safruddin</t>
+          <t>Dr. Aisjah Farhum</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1063,7 +1059,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Marine Fisheries</t>
+          <t>Fishing vessel engineering</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1073,12 +1069,12 @@
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6005214</t>
+          <t>6005387</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57195941084</t>
+          <t>57195941968</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,22 +1089,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Madya. Muzzneena Ahmad Mustapha</t>
+          <t>Prof. Safruddin</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Universiti Kebangsaan Malaysia (UKM)</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Marine Remote sensing and GIS</t>
+          <t>Marine Fisheries</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1116,8 +1112,16 @@
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>6005214</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>57195941084</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1130,22 +1134,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Toshihide Kitakado</t>
+          <t>Prof. Madya. Muzzneena Ahmad Mustapha</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Tokyo University of Marine Science and Technology</t>
+          <t>Universiti Kebangsaan Malaysia (UKM)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Stock assessment and management, spatial prediction of tunas</t>
+          <t>Marine Remote sensing and GIS</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1154,11 +1158,7 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>14010144100</t>
-        </is>
-      </c>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1171,22 +1171,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Xuefeng Wang</t>
+          <t>Prof. Toshihide Kitakado</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Guangdong Ocean University</t>
+          <t>Tokyo University of Marine Science and Technology</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Fisheries resource ecology and ecosystem-based management</t>
+          <t>Stock assessment and management, spatial prediction of tunas</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1197,7 +1197,7 @@
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>55736859000</t>
+          <t>14010144100</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1212,22 +1212,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Andi Risda Fitrianti Abudarda, M.Si.</t>
+          <t>Prof. Xuefeng Wang</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Guangdong Ocean University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Fisheries GIS</t>
+          <t>Fisheries resource ecology and ecosystem-based management</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1236,7 +1236,11 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>55736859000</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1249,12 +1253,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Siti Khadijah Srioktoviana</t>
+          <t>Andi Risda Fitrianti Abudarda, M.Si.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Student</t>
+          <t>Fisheries GIS</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1273,11 +1277,7 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>59311317100</t>
-        </is>
-      </c>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Alfira Yuniar</t>
+          <t>Siti Khadijah Srioktoviana</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1316,7 +1316,7 @@
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>57226725862</t>
+          <t>59311317100</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Andi Mutmainna Qalbi</t>
+          <t>Alfira Yuniar</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Master Student</t>
+          <t>Doctoral Student</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1355,7 +1355,11 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>57226725862</t>
+        </is>
+      </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1368,12 +1372,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Amaliah Ramadhani</t>
+          <t>Andi Mutmainna Qalbi</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1405,12 +1409,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Anugrah</t>
+          <t>Amaliah Ramadhani</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1442,12 +1446,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fakhruddin Rifaldi</t>
+          <t>Anugrah</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1477,10 +1481,26 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Muhammad Fakhruddin Rifaldi</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Master Student</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>The Tuna Fisheries and Economic Development Research Group focuses on advancing knowledge and collaboration in the field of tuna fisheries, emphasizing sustainable management and economic growth. Our mission is to develop research, education, and scientific publications in partnership with global stakeholders. Through interdisciplinary collaboration, we aim to enhance productivity in research, teaching, and publications related to tuna fisheries and their economic impact. By addressing key challenges such as overfishing, market sustainability, and policy development, our group contributes to long-term socio-economic benefits while ensuring the preservation of marine ecosystems for future generations.</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1488,7 +1508,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1677,15 +1701,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
